--- a/frontend/public/templates/sample_image_subjective_upload.xlsx
+++ b/frontend/public/templates/sample_image_subjective_upload.xlsx
@@ -26,8 +26,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="3">
@@ -39,12 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004F81BD"/>
-        <bgColor rgb="004F81BD"/>
+        <fgColor rgb="00F96331"/>
+        <bgColor rgb="00F96331"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -52,15 +54,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,15 +435,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="82" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="102" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,62 +479,32 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>PHY</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BEGINNER</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>APTITUDE</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>FRESHER</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Define Newton's first law of motion.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>newton_law.jpg</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>An object at rest stays at rest...</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BIO</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>INTERMEDIATE</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Explain the process of photosynthesis.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>photosynthesis.png</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Photosynthesis is a process used by plants...</t>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Based on the image, describe the primary characteristics of the feline shown.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>beautiful-cat.png</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a beautiful cat with white fur and striking blue eyes, sitting in a calm posture.</t>
         </is>
       </c>
     </row>

--- a/frontend/public/templates/sample_image_subjective_upload.xlsx
+++ b/frontend/public/templates/sample_image_subjective_upload.xlsx
@@ -26,10 +26,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="13"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
@@ -41,8 +40,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F96331"/>
-        <bgColor rgb="00F96331"/>
+        <fgColor rgb="00f96331"/>
+        <bgColor rgb="00f96331"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,12 +63,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,9 +436,9 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="82" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="102" customWidth="1" min="6" max="6"/>
@@ -479,30 +477,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>APTITUDE</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Based on the image, describe the primary characteristics of the feline shown.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>beautiful-cat.png</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>The image shows a beautiful cat with white fur and striking blue eyes, sitting in a calm posture.</t>
         </is>

--- a/frontend/public/templates/sample_image_subjective_upload.xlsx
+++ b/frontend/public/templates/sample_image_subjective_upload.xlsx
@@ -54,19 +54,30 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -433,15 +444,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="82" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="102" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,7 +464,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Level Code</t>
+          <t>Exam Level Code</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -473,36 +485,186 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Model Answer</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Answer Explanation</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>APTITUDE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>INDUSTRY_AWARENESS</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Based on the image, describe the primary characteristics of the feline shown.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>beautiful-cat.png</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>The image shows a beautiful cat with white fur and striking blue eyes, sitting in a calm posture.</t>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Observe the industry trend in image 1 and provide a summary.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_1.png</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>The trend indicates a shift towards sustainable practices in the 1 sector...</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Assessing observational skills and market knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>INDUSTRY_AWARENESS</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>FRESHER</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Observe the industry trend in image 2 and provide a summary.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_2.png</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>The trend indicates a shift towards sustainable practices in the 2 sector...</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Assessing observational skills and market knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>INDUSTRY_AWARENESS</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>FRESHER</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Observe the industry trend in image 3 and provide a summary.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_3.png</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>The trend indicates a shift towards sustainable practices in the 3 sector...</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Assessing observational skills and market knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>INDUSTRY_AWARENESS</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>FRESHER</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Observe the industry trend in image 4 and provide a summary.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_4.png</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>The trend indicates a shift towards sustainable practices in the 4 sector...</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Assessing observational skills and market knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>INDUSTRY_AWARENESS</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>FRESHER</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Observe the industry trend in image 5 and provide a summary.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_5.png</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>The trend indicates a shift towards sustainable practices in the 5 sector...</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Assessing observational skills and market knowledge.</t>
         </is>
       </c>
     </row>

--- a/frontend/public/templates/sample_image_subjective_upload.xlsx
+++ b/frontend/public/templates/sample_image_subjective_upload.xlsx
@@ -451,7 +451,7 @@
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
@@ -509,14 +509,10 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Observe the industry trend in image 1 and provide a summary.</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>data_chart_1.png</t>
-        </is>
-      </c>
+          <t>Observe the industry trend in scenario 1 and provide a summary.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>The trend indicates a shift towards sustainable practices in the 1 sector...</t>
@@ -544,14 +540,10 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Observe the industry trend in image 2 and provide a summary.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>data_chart_2.png</t>
-        </is>
-      </c>
+          <t>Observe the industry trend in scenario 2 and provide a summary.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>The trend indicates a shift towards sustainable practices in the 2 sector...</t>
@@ -579,14 +571,10 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Observe the industry trend in image 3 and provide a summary.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>data_chart_3.png</t>
-        </is>
-      </c>
+          <t>Observe the industry trend in scenario 3 and provide a summary.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>The trend indicates a shift towards sustainable practices in the 3 sector...</t>
@@ -614,14 +602,10 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Observe the industry trend in image 4 and provide a summary.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>data_chart_4.png</t>
-        </is>
-      </c>
+          <t>Observe the industry trend in scenario 4 and provide a summary.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>The trend indicates a shift towards sustainable practices in the 4 sector...</t>
@@ -649,14 +633,10 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Observe the industry trend in image 5 and provide a summary.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>data_chart_5.png</t>
-        </is>
-      </c>
+          <t>Observe the industry trend in scenario 5 and provide a summary.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>The trend indicates a shift towards sustainable practices in the 5 sector...</t>

--- a/frontend/public/templates/sample_image_subjective_upload.xlsx
+++ b/frontend/public/templates/sample_image_subjective_upload.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,7 +512,11 @@
           <t>Observe the industry trend in scenario 1 and provide a summary.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_1.png</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>The trend indicates a shift towards sustainable practices in the 1 sector...</t>
@@ -543,7 +547,11 @@
           <t>Observe the industry trend in scenario 2 and provide a summary.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_2.png</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>The trend indicates a shift towards sustainable practices in the 2 sector...</t>
@@ -574,7 +582,11 @@
           <t>Observe the industry trend in scenario 3 and provide a summary.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_3.png</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>The trend indicates a shift towards sustainable practices in the 3 sector...</t>
@@ -605,7 +617,11 @@
           <t>Observe the industry trend in scenario 4 and provide a summary.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_4.png</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>The trend indicates a shift towards sustainable practices in the 4 sector...</t>
@@ -636,7 +652,11 @@
           <t>Observe the industry trend in scenario 5 and provide a summary.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_5.png</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>The trend indicates a shift towards sustainable practices in the 5 sector...</t>

--- a/frontend/public/templates/sample_image_subjective_upload.xlsx
+++ b/frontend/public/templates/sample_image_subjective_upload.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,8 +30,19 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF333333"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,8 +55,13 @@
         <bgColor rgb="00f96331"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF96331"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -67,16 +83,57 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
+    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -444,225 +501,236 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Question Id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Subject Code</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Exam Level Code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Question Text</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Question Image</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Model Answer</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Answer Explanation</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>INDUSTRY_AWARENESS</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="D2" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Observe the industry trend in scenario 1 and provide a summary.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>data_chart_1.png</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>The trend indicates a shift towards sustainable practices in the 1 sector...</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>Assessing observational skills and market knowledge.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>INDUSTRY_AWARENESS</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="D3" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Observe the industry trend in scenario 2 and provide a summary.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>data_chart_2.png</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>The trend indicates a shift towards sustainable practices in the 2 sector...</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Assessing observational skills and market knowledge.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>INDUSTRY_AWARENESS</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="D4" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Observe the industry trend in scenario 3 and provide a summary.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>data_chart_3.png</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>The trend indicates a shift towards sustainable practices in the 3 sector...</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Assessing observational skills and market knowledge.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>INDUSTRY_AWARENESS</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="D5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Observe the industry trend in scenario 4 and provide a summary.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>data_chart_4.png</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>The trend indicates a shift towards sustainable practices in the 4 sector...</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Assessing observational skills and market knowledge.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>INDUSTRY_AWARENESS</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="D6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Observe the industry trend in scenario 5 and provide a summary.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>data_chart_5.png</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>The trend indicates a shift towards sustainable practices in the 5 sector...</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Assessing observational skills and market knowledge.</t>
         </is>
